--- a/stories/arbres/ATOM-SOC.CUI.001-02.xlsx
+++ b/stories/arbres/ATOM-SOC.CUI.001-02.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Le soir, Ava entre dans la cuisine. Papa met la nappe. Ava dit : je peux aider ? Papa dit : oui. Une tâche sûre, avec un adulte. Papa, c'est l'adulte. Ava ouvre le robinet. Elle lave une tomate rouge. L'eau coule. La peau brille. Alors la tomate est propre. Ava l'essuie. Papa pose les assiettes. Ava prend une cuillère. Elle pose la cuillère près de chaque assiette. Alors chacun a sa cuillère. Ava va au panier. Elle apporte le pain. Elle le pose au milieu. Alors le pain est à table. Papa dit : merci. Laver, poser, apporter. Ava reste près de papa. Ensemble, ils appellent maman.</t>
+          <t>Le soir, Ava entre dans la cuisine. Papa met la nappe. Je peux aider ? Oui. Une tâche sûre, avec un adulte. Papa, c'est l'adulte. Ava ouvre le robinet. Elle lave une tomate rouge. L'eau coule. La peau brille. Alors la tomate est propre. Ava l'essuie. Papa pose les assiettes. Ava prend une cuillère. Elle pose la cuillère près de chaque assiette. Alors chacun a sa cuillère. Ava va au panier. Elle apporte le pain. Elle le pose au milieu. Alors le pain est à table. Merci. Laver, poser, apporter. Ava reste près de papa. Ensemble, ils appellent maman.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,16 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Le soir, Ava entre dans la cuisine. Papa met la nappe.
+enfant-f|Je peux aider ?
+papa|Oui.
+narrateur|Une tâche sûre, avec un adulte. Papa, c'est l'adulte. Ava ouvre le robinet. Elle lave une tomate rouge. L'eau coule. La peau brille. Alors la tomate est propre. Ava l'essuie. Papa pose les assiettes. Ava prend une cuillère. Elle pose la cuillère près de chaque assiette. Alors chacun a sa cuillère. Ava va au panier. Elle apporte le pain. Elle le pose au milieu. Alors le pain est à table.
+papa|Merci. Laver, poser, apporter.
+narrateur|Ava reste près de papa. Ensemble, ils appellent maman.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1469,6 +1495,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Ava prépare avec papa. Que fait-elle ?</t>
         </is>
       </c>
     </row>
@@ -1637,6 +1668,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Ava a lavé la tomate. Elle a posé les cuillères. Elle a apporté le pain. Avec papa. Une tâche sûre.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1795,6 +1831,11 @@
         <v>8</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Toute la famille s'assoit. Ava croque la tomate. Elle est fraîche.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1957,6 +1998,11 @@
         <v>8</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1975,7 +2021,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1992,6 +2038,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SOC.CUI.001-02.xlsx
+++ b/stories/arbres/ATOM-SOC.CUI.001-02.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1315,6 +1320,7 @@
 narrateur|Ava reste près de papa. Ensemble, ils appellent maman.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1502,6 +1508,7 @@
           <t>narrateur|Ava prépare avec papa. Que fait-elle ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1673,6 +1680,7 @@
           <t>narrateur|Ava a lavé la tomate. Elle a posé les cuillères. Elle a apporté le pain. Avec papa. Une tâche sûre.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1836,6 +1844,7 @@
           <t>narrateur|Toute la famille s'assoit. Ava croque la tomate. Elle est fraîche.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2003,6 +2012,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2021,7 +2031,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2045,6 +2055,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2059,7 +2083,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2246,6 +2270,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-SOC.CUI.001-02.xlsx
+++ b/stories/arbres/ATOM-SOC.CUI.001-02.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Ava prépare le dîner avec papa</t>
+          <t>Les croûtons d'Amir</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Amir veut une soupe avec des croûtons. Un cube tombe. Le chat le regarde. Ils en font un autre. La vapeur danse. Ils croquent.</t>
         </is>
       </c>
     </row>
@@ -1172,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Le soir, Ava entre dans la cuisine. Papa met la nappe. Je peux aider ? Oui. Une tâche sûre, avec un adulte. Papa, c'est l'adulte. Ava ouvre le robinet. Elle lave une tomate rouge. L'eau coule. La peau brille. Alors la tomate est propre. Ava l'essuie. Papa pose les assiettes. Ava prend une cuillère. Elle pose la cuillère près de chaque assiette. Alors chacun a sa cuillère. Ava va au panier. Elle apporte le pain. Elle le pose au milieu. Alors le pain est à table. Merci. Laver, poser, apporter. Ava reste près de papa. Ensemble, ils appellent maman.</t>
+          <t>La casserole chante tout bas. Un nuage monte vers le plafond. La fenêtre s'embue un peu. Ça sent la carotte et le thym. Tu as entendu la casserole, Amir ? Elle chante. Oui. La soupe est presque prête. En ce moment, Amir veut des croûtons. Je veux des cubes dans la soupe. On les fait ensemble ? Oui. Je peux aider ? Oui, avec moi. Papa pose une planche près du feu. Le pain est un peu rassis. Amir le tient des deux mains. Papa coupe, tout doux. Amir range les cubes dans l'assiette. Ils sont durs. Ils vont dorer. Un cube glisse du bord. Il tombe près de la chaise. Le chat s'approche, tout silencieux. Il regarde le cube par terre. Il le veut ! On en fait un autre ? Oui. Amir prend un bout de pain. Papa l'aide à le couper. Le nouveau cube rejoint l'assiette. Merci, Amir. Tu as aidé. Les cubes vont dans la poêle. Ils font un petit bruit. Ça sent le pain chaud. Ils dorent. Tu les vois devenir dorés ? Oui. Le chat reste près de la chaise. Le cube tombé ne bouge plus. Papa verse la soupe dans deux bols. La vapeur danse au-dessus. Je mets les croûtons ? Oui. Amir pose trois cubes dans son bol. Ils flottent, puis s'enfoncent. On s'assoit près de la fenêtre ? Oui. La vitre est un peu blanche. Dehors, le jardin devient bleu. Amir souffle sur la vapeur. C'est chaud. On attend un peu. Le chat saute sur le rebord. Il regarde encore le cube. Il a son croûton, lui. Et toi, tu as les tiens. Amir croque un cube. Ça fait un bruit net. C'est bon. La soupe sent le thym. Amir plonge la cuillère. Un croûton revient, tout mouillé. Il a bu la soupe. Oui. La casserole se tait sur le feu. Le chat se lèche la patte.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Le soir, Ava entre dans la cuisine. Papa met la nappe. Ava dit : je peux aider ? Papa dit : oui. Une &lt;emphasis level="moderate"&gt;tâche&lt;/emphasis&gt; sûre, avec un adulte. Papa, c'est l'adulte. Ava ouvre le robinet. Elle lave une tomate rouge. L'eau coule. La peau brille. Alors la tomate est propre. Ava l'essuie. Papa pose les assiettes. Ava prend une cuillère. Elle pose la cuillère près de chaque assiette. Alors chacun a sa cuillère. Ava va au panier. Elle apporte le pain. Elle le pose au milieu. Alors le pain est à table. Papa dit : merci. Laver, poser, apporter. Ava reste près de papa. Ensemble, ils appellent maman.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>La casserole chante tout bas. Un nuage monte vers le plafond. La fenêtre s'embue un peu. Ça sent la carotte et le thym. Tu as entendu la casserole, Amir ? Elle chante. Oui. La soupe est presque prête. En ce moment, Amir veut des croûtons. Je veux des cubes dans la soupe. On les fait ensemble ? Oui. Je peux aider ? Oui, avec moi. Papa pose une planche près du feu. Le pain est un peu rassis. Amir le tient des deux mains. Papa coupe, tout doux. Amir range les cubes dans l'assiette. Ils sont durs. Ils vont dorer. Un cube glisse du bord. Il tombe près de la chaise. Le chat s'approche, tout silencieux. Il regarde le cube par terre. Il le veut ! On en fait un autre ? Oui. Amir prend un bout de pain. Papa l'aide à le couper. Le nouveau cube rejoint l'assiette. Merci, Amir. Tu as aidé. Les cubes vont dans la poêle. Ils font un petit bruit. Ça sent le pain chaud. Ils dorent. Tu les vois devenir dorés ? Oui. Le chat reste près de la chaise. Le cube tombé ne bouge plus. Papa verse la soupe dans deux bols. La vapeur danse au-dessus. Je mets les croûtons ? Oui. Amir pose trois cubes dans son bol. Ils flottent, puis s'enfoncent. On s'assoit près de la fenêtre ? Oui. La vitre est un peu blanche. Dehors, le jardin devient bleu. Amir souffle sur la vapeur. C'est chaud. On attend un peu. Le chat saute sur le rebord. Il regarde encore le cube. Il a son croûton, lui. Et toi, tu as les tiens. Amir croque un cube. Ça fait un bruit net. C'est bon. La soupe sent le thym. Amir plonge la cuillère. Un croûton revient, tout mouillé. Il a bu la soupe. Oui. La casserole se tait sur le feu. Le chat se lèche la patte.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1240,7 +1252,7 @@
         <v>0.92</v>
       </c>
       <c r="AB2" s="2" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
@@ -1312,15 +1324,76 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Le soir, Ava entre dans la cuisine. Papa met la nappe.
-enfant-f|Je peux aider ?
+          <t>narrateur|La casserole chante tout bas.
+narrateur|Un nuage monte vers le plafond.
+narrateur|La fenêtre s'embue un peu.
+narrateur|Ça sent la carotte et le thym.
+papa|Tu as entendu la casserole, Amir ?
+enfant-m|Elle chante.
 papa|Oui.
-narrateur|Une tâche sûre, avec un adulte. Papa, c'est l'adulte. Ava ouvre le robinet. Elle lave une tomate rouge. L'eau coule. La peau brille. Alors la tomate est propre. Ava l'essuie. Papa pose les assiettes. Ava prend une cuillère. Elle pose la cuillère près de chaque assiette. Alors chacun a sa cuillère. Ava va au panier. Elle apporte le pain. Elle le pose au milieu. Alors le pain est à table.
-papa|Merci. Laver, poser, apporter.
-narrateur|Ava reste près de papa. Ensemble, ils appellent maman.</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr"/>
+papa|La soupe est presque prête.
+narrateur|En ce moment, Amir veut des croûtons.
+enfant-m|Je veux des cubes dans la soupe.
+papa|On les fait ensemble ?
+enfant-m|Oui.
+enfant-m|Je peux aider ?
+papa|Oui, avec moi.
+narrateur|Papa pose une planche près du feu.
+narrateur|Le pain est un peu rassis.
+narrateur|Amir le tient des deux mains.
+narrateur|Papa coupe, tout doux.
+narrateur|Amir range les cubes dans l'assiette.
+enfant-m|Ils sont durs.
+papa|Ils vont dorer.
+narrateur|Un cube glisse du bord.
+narrateur|Il tombe près de la chaise.
+narrateur|Le chat s'approche, tout silencieux.
+narrateur|Il regarde le cube par terre.
+enfant-m|Il le veut !
+papa|On en fait un autre ?
+enfant-m|Oui.
+narrateur|Amir prend un bout de pain.
+narrateur|Papa l'aide à le couper.
+narrateur|Le nouveau cube rejoint l'assiette.
+papa|Merci, Amir.
+papa|Tu as aidé.
+narrateur|Les cubes vont dans la poêle.
+narrateur|Ils font un petit bruit.
+narrateur|Ça sent le pain chaud.
+enfant-m|Ils dorent.
+papa|Tu les vois devenir dorés ?
+enfant-m|Oui.
+narrateur|Le chat reste près de la chaise.
+narrateur|Le cube tombé ne bouge plus.
+narrateur|Papa verse la soupe dans deux bols.
+narrateur|La vapeur danse au-dessus.
+enfant-m|Je mets les croûtons ?
+papa|Oui.
+narrateur|Amir pose trois cubes dans son bol.
+narrateur|Ils flottent, puis s'enfoncent.
+papa|On s'assoit près de la fenêtre ?
+enfant-m|Oui.
+narrateur|La vitre est un peu blanche.
+narrateur|Dehors, le jardin devient bleu.
+narrateur|Amir souffle sur la vapeur.
+enfant-m|C'est chaud.
+papa|On attend un peu.
+narrateur|Le chat saute sur le rebord.
+narrateur|Il regarde encore le cube.
+enfant-m|Il a son croûton, lui.
+papa|Et toi, tu as les tiens.
+narrateur|Amir croque un cube.
+narrateur|Ça fait un bruit net.
+enfant-m|C'est bon.
+papa|La soupe sent le thym.
+narrateur|Amir plonge la cuillère.
+narrateur|Un croûton revient, tout mouillé.
+enfant-m|Il a bu la soupe.
+papa|Oui.
+narrateur|La casserole se tait sur le feu.
+narrateur|Le chat se lèche la patte.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1345,12 +1418,12 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Ava prépare avec papa. Que fait-elle ?</t>
+          <t>Amir prépare la soupe avec papa. Que fait-il ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Ava prépare &lt;emphasis level="moderate"&gt;avec&lt;/emphasis&gt; papa. Que fait-elle ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Amir prépare la soupe avec papa. Que fait-il ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1365,7 +1438,7 @@
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>aider | laver | poser | avec papa</t>
+          <t>aider | les croûtons | il aide | avec papa | les cubes | la soupe</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
@@ -1380,7 +1453,7 @@
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>Elle pose la cuillère. Que fait Ava ?</t>
+          <t>Amir aide papa. Que fait-il ?</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr"/>
@@ -1429,7 +1502,7 @@
         <v>0.86</v>
       </c>
       <c r="AB3" s="2" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
@@ -1505,10 +1578,10 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Ava prépare avec papa. Que fait-elle ?</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr"/>
+          <t>narrateur|Amir prépare la soupe avec papa.
+narrateur|Que fait-il ?</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1533,12 +1606,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Ava a lavé la tomate. Elle a posé les cuillères. Elle a apporté le pain. Avec papa. Une tâche sûre.</t>
+          <t>Amir a rangé les cubes. Un croûton est tombé. Le chat l'a regardé. Ils en ont fait un autre. Tu as aidé, Amir. J'ai mis les croûtons. Oui. La vapeur danse encore. Le bol sent le thym.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Ava a lavé la tomate. Elle a posé les cuillères. Elle a apporté le pain. Avec papa. Une &lt;emphasis level="moderate"&gt;tâche&lt;/emphasis&gt; sûre.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Amir a rangé les cubes. Un croûton est tombé. Le chat l'a regardé. Ils en ont fait un autre. Tu as aidé, Amir. J'ai mis les croûtons. Oui. La vapeur danse encore. Le bol sent le thym.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1601,7 +1674,7 @@
         <v>0.92</v>
       </c>
       <c r="AB4" s="2" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
@@ -1677,10 +1750,17 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Ava a lavé la tomate. Elle a posé les cuillères. Elle a apporté le pain. Avec papa. Une tâche sûre.</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr"/>
+          <t>narrateur|Amir a rangé les cubes.
+narrateur|Un croûton est tombé.
+narrateur|Le chat l'a regardé.
+narrateur|Ils en ont fait un autre.
+papa|Tu as aidé, Amir.
+enfant-m|J'ai mis les croûtons.
+papa|Oui.
+narrateur|La vapeur danse encore.
+narrateur|Le bol sent le thym.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1705,12 +1785,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Toute la famille s'assoit. Ava croque la tomate. Elle est fraîche.</t>
+          <t>Amir pose sa cuillère. Il reste un croûton ? Le dernier. Il le pousse dans la soupe. Il croque, tout chaud. Merci pour les cubes. Le chat a le sien. Oui, par terre. La fenêtre reste un peu blanche. Le jardin est presque noir.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Toute la famille s'assoit. Ava croque la tomate. Elle est fraîche.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Amir pose sa cuillère. Il reste un croûton ? Le dernier. Il le pousse dans la soupe. Il croque, tout chaud. Merci pour les cubes. Le chat a le sien. Oui, par terre. La fenêtre reste un peu blanche. Le jardin est presque noir.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1773,7 +1853,7 @@
         <v>0.92</v>
       </c>
       <c r="AB5" s="2" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
@@ -1841,10 +1921,18 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Toute la famille s'assoit. Ava croque la tomate. Elle est fraîche.</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr"/>
+          <t>narrateur|Amir pose sa cuillère.
+papa|Il reste un croûton ?
+enfant-m|Le dernier.
+narrateur|Il le pousse dans la soupe.
+narrateur|Il croque, tout chaud.
+papa|Merci pour les cubes.
+enfant-m|Le chat a le sien.
+papa|Oui, par terre.
+narrateur|La fenêtre reste un peu blanche.
+narrateur|Le jardin est presque noir.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1869,12 +1957,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Amir souffle une dernière vapeur. La soupe était bonne. Oui. Le chat s'endort près de la chaise. Le bol tiède sent encore le thym.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>Amir souffle une dernière vapeur. La soupe était bonne. Oui. Le chat s'endort près de la chaise. Le bol tiède sent encore le thym.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -1930,14 +2018,14 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>slow</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="AA6" s="2" t="n">
         <v>0.88</v>
       </c>
       <c r="AB6" s="2" t="n">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
@@ -2009,10 +2097,13 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+          <t>narrateur|Amir souffle une dernière vapeur.
+enfant-m|La soupe était bonne.
+papa|Oui.
+narrateur|Le chat s'endort près de la chaise.
+narrateur|Le bol tiède sent encore le thym.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2031,7 +2122,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2069,6 +2160,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SOC.CUI.001-02.xlsx
+++ b/stories/arbres/ATOM-SOC.CUI.001-02.xlsx
@@ -671,7 +671,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>cuisine</t>
+          <t>cuisine le soir, casserole et chat</t>
         </is>
       </c>
     </row>
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Ava, papa</t>
+          <t>Amir, papa</t>
         </is>
       </c>
     </row>
